--- a/data/ams_weekly_data/Tonor/business_report_week24.xlsx
+++ b/data/ams_weekly_data/Tonor/business_report_week24.xlsx
@@ -578,10 +578,10 @@
         <v>11</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>0.0038</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>0.0047</v>
       </c>
       <c r="J2" t="n">
         <v>674</v>
@@ -590,13 +590,13 @@
         <v>12</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>0.0046</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>0.0038</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>0.0103</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -659,10 +659,10 @@
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>0.0012</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>0.0009</v>
       </c>
       <c r="J3" t="n">
         <v>200</v>
@@ -671,13 +671,13 @@
         <v>2</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>0.0014</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>0.0508</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -740,10 +740,10 @@
         <v>5</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>0.0007</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>0.0021</v>
       </c>
       <c r="J4" t="n">
         <v>116</v>
@@ -752,13 +752,13 @@
         <v>7</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>0.0008</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>0.0022</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>0.0095</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -821,10 +821,10 @@
         <v>9</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>0.0041</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>0.0039</v>
       </c>
       <c r="J5" t="n">
         <v>636</v>
@@ -833,31 +833,31 @@
         <v>15</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>0.0043</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>0.0047</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>0.0103</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>0.0021</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>6793.216949152542</v>
+        <v>8487.286949152543</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -902,10 +902,10 @@
         <v>3</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>0.0013</v>
       </c>
       <c r="J6" t="n">
         <v>105</v>
@@ -914,13 +914,13 @@
         <v>3</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>0.0007</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>0.0009</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>0.303</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -932,7 +932,7 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>0.0149</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1070,7 +1070,7 @@
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1133,10 +1133,10 @@
         <v>10</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>0.004</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>0.0043</v>
       </c>
       <c r="J9" t="n">
         <v>641</v>
@@ -1145,31 +1145,31 @@
         <v>14</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>0.0044</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>0.0044</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>0.0339</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>0.0022</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>22381.36338983051</v>
+        <v>26108.48338983051</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -1214,10 +1214,10 @@
         <v>21</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>0.0018</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="J10" t="n">
         <v>272</v>
@@ -1226,19 +1226,19 @@
         <v>31</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>0.0019</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>0.0098</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>0.224</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -1250,7 +1250,7 @@
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>7624.59</v>
+        <v>10166.12</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
@@ -1287,7 +1287,7 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>0.0004</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -1299,13 +1299,13 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>0.0004</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>0.0204</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1360,7 +1360,7 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -1372,7 +1372,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -1433,7 +1433,7 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>0.0005</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -1445,13 +1445,13 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>0.2632</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -1463,7 +1463,7 @@
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>0.0161</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -1506,10 +1506,10 @@
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>0.0003</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>0.0004</v>
       </c>
       <c r="J14" t="n">
         <v>53</v>
@@ -1518,10 +1518,10 @@
         <v>1</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>0.0004</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>0.0003</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -1579,7 +1579,7 @@
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>0.0002</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -1591,13 +1591,13 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>0.0002</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>0.09089999999999999</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -1652,10 +1652,10 @@
         <v>2</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>0.0009</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>0.0009</v>
       </c>
       <c r="J16" t="n">
         <v>156</v>
@@ -1664,13 +1664,13 @@
         <v>2</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>0.0011</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>0.0949</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -1733,10 +1733,10 @@
         <v>5</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>0.0012</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>0.0021</v>
       </c>
       <c r="J17" t="n">
         <v>188</v>
@@ -1745,13 +1745,13 @@
         <v>7</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>0.0013</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>0.0022</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>0.0465</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -1824,7 +1824,7 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -1887,10 +1887,10 @@
         <v>18</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>0.0055</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>0.0077</v>
       </c>
       <c r="J19" t="n">
         <v>968</v>
@@ -1899,19 +1899,19 @@
         <v>22</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>0.0066</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>0.0069</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>0.0046</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -1923,7 +1923,7 @@
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>23716.95</v>
+        <v>28799.14</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
@@ -1968,10 +1968,10 @@
         <v>3</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>0.0004</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>0.0013</v>
       </c>
       <c r="J20" t="n">
         <v>64</v>
@@ -1980,10 +1980,10 @@
         <v>3</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>0.0004</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>0.0009</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -2049,10 +2049,10 @@
         <v>4</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>0.0003</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>0.0017</v>
       </c>
       <c r="J21" t="n">
         <v>45</v>
@@ -2061,16 +2061,16 @@
         <v>4</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>0.0003</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>0.0013</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P21" t="n">
         <v>1</v>
@@ -2079,7 +2079,7 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>0.0278</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -2140,7 +2140,7 @@
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -2203,10 +2203,10 @@
         <v>2</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>0.0009</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>0.0009</v>
       </c>
       <c r="J23" t="n">
         <v>145</v>
@@ -2215,13 +2215,13 @@
         <v>4</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>0.0013</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>0.0313</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -2284,10 +2284,10 @@
         <v>5</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>0.0024</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>0.0021</v>
       </c>
       <c r="J24" t="n">
         <v>379</v>
@@ -2296,10 +2296,10 @@
         <v>8</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>0.0026</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>0.0025</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
@@ -2308,7 +2308,7 @@
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -2320,7 +2320,7 @@
         <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>6776.28</v>
+        <v>8470.35</v>
       </c>
       <c r="U24" t="n">
         <v>0</v>
@@ -2365,10 +2365,10 @@
         <v>7</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>0.0013</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>0.003</v>
       </c>
       <c r="J25" t="n">
         <v>194</v>
@@ -2377,13 +2377,13 @@
         <v>8</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>0.0013</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>0.0025</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>0.0615</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
